--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLÍNICA PONFERRADA SDP.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLÍNICA PONFERRADA SDP.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2.912</v>
+        <v>3.031</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6964</v>
+        <v>2.0768</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2156</v>
+        <v>0.9542</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8278</v>
+        <v>3.8673</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3384</v>
+        <v>1.3626</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4894</v>
+        <v>2.5045</v>
       </c>
       <c r="J2" t="n">
-        <v>6.779500000000001</v>
+        <v>6.9799</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1481</v>
+        <v>2.2672</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6313</v>
+        <v>4.7128</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9517</v>
+        <v>-3.1128</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8098000000000001</v>
+        <v>-0.9044</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1419</v>
+        <v>-2.2082</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4824</v>
+        <v>3.4417</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1223</v>
+        <v>-2.0989</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.3976</v>
+        <v>-3.3193</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2751</v>
+        <v>1.2204</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8453</v>
+        <v>2.8823</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4356</v>
+        <v>3.4774</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7044</v>
+        <v>2.7383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2393999999999998</v>
+        <v>0.5725</v>
       </c>
       <c r="F3" t="n">
-        <v>2.465</v>
+        <v>2.1657</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4548</v>
+        <v>1.5033</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2801</v>
+        <v>1.3223</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1747000000000001</v>
+        <v>0.181</v>
       </c>
       <c r="J3" t="n">
-        <v>2.45</v>
+        <v>2.6381</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8073999999999999</v>
+        <v>0.9232</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6427</v>
+        <v>1.7149</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9953999999999998</v>
+        <v>-1.1347</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4727</v>
+        <v>0.3991</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.468</v>
+        <v>-1.5339</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R3" t="n">
-        <v>4.3018</v>
+        <v>4.2515</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0195</v>
+        <v>1.0098</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1024</v>
+        <v>-1.0406</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1219</v>
+        <v>2.0503</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2302</v>
+        <v>0.2251000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1936</v>
+        <v>3.2264</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.9634</v>
+        <v>-3.0013</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.663</v>
+        <v>2.6916</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2789</v>
+        <v>3.3732</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6158</v>
+        <v>-0.6816</v>
       </c>
       <c r="G4" t="n">
-        <v>2.023</v>
+        <v>2.0476</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1503</v>
+        <v>-0.139</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1733</v>
+        <v>2.1865</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6004</v>
+        <v>2.6487</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4568</v>
+        <v>-0.4359</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0572</v>
+        <v>3.0846</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5774</v>
+        <v>-0.6011</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3065</v>
+        <v>0.297</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8838</v>
+        <v>-0.8981</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3775</v>
+        <v>1.3729</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3043</v>
+        <v>1.3079</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0732</v>
+        <v>0.065</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8975</v>
+        <v>0.8485</v>
       </c>
       <c r="E5" t="n">
-        <v>1.48</v>
+        <v>1.5514</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5825</v>
+        <v>-0.7029</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0265</v>
+        <v>-1.0544</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1289</v>
+        <v>-0.1456</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0433</v>
+        <v>1.074</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3396999999999999</v>
+        <v>-0.3174000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.383</v>
+        <v>1.3914</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0698</v>
+        <v>-2.1284</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5579000000000001</v>
+        <v>-0.5912999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5119</v>
+        <v>-1.5371</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2049</v>
+        <v>-0.2024</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8193</v>
+        <v>0.8099000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1289</v>
+        <v>2.1052</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9768000000000001</v>
+        <v>0.9877</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1521</v>
+        <v>1.1175</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09949999999999992</v>
+        <v>0.1926999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7945</v>
+        <v>-2.4535</v>
       </c>
       <c r="F6" t="n">
-        <v>2.894</v>
+        <v>2.6461</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2376</v>
+        <v>-2.2028</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2167</v>
+        <v>-1.1311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.021</v>
+        <v>-1.0716</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0625</v>
+        <v>0.2157</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9649000000000001</v>
+        <v>-0.8180000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0274</v>
+        <v>1.0336</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3001</v>
+        <v>-2.4184</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2518</v>
+        <v>-0.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0483</v>
+        <v>-2.1053</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6872</v>
+        <v>-3.6442</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.3745</v>
+        <v>-7.2883</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6873</v>
+        <v>3.6441</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7516</v>
+        <v>3.7136</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9460999999999999</v>
+        <v>0.9839</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8056</v>
+        <v>2.7297</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2729</v>
+        <v>2.3258</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5715</v>
+        <v>3.6351</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5182</v>
+        <v>-0.5826</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.475</v>
+        <v>-1.4143</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9567999999999999</v>
+        <v>0.8318</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.813</v>
+        <v>-1.8201</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7756</v>
+        <v>-1.7789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03739999999999988</v>
+        <v>-0.0411999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0582</v>
+        <v>-1.0179</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7195</v>
+        <v>-1.7009</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6613000000000001</v>
+        <v>0.6830999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7548</v>
+        <v>-0.8022</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05610000000000001</v>
+        <v>-0.0779</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6987</v>
+        <v>-0.7242999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2583</v>
+        <v>1.2388</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2119</v>
+        <v>-0.194</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4701</v>
+        <v>1.4328</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1925</v>
+        <v>-1.216</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1925</v>
+        <v>-1.216</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5708</v>
+        <v>-0.6066</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1385</v>
+        <v>0.2034</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7093</v>
+        <v>-0.8099000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.02150000000000007</v>
+        <v>-0.0444</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3875999999999999</v>
+        <v>-0.395</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3661</v>
+        <v>0.3505</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6778</v>
+        <v>0.7176</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03109999999999996</v>
+        <v>0.058</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6468</v>
+        <v>0.6596</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6993</v>
+        <v>-0.7619</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4186</v>
+        <v>-0.4529</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2806</v>
+        <v>-0.3091</v>
       </c>
       <c r="P8" t="n">
-        <v>1.229</v>
+        <v>1.2148</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5978</v>
+        <v>-0.5867</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3345</v>
+        <v>-0.3117</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2634</v>
+        <v>-0.2749</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7852</v>
+        <v>-2.7881</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1371000000000002</v>
+        <v>0.2524000000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9223</v>
+        <v>-3.0405</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1831</v>
+        <v>0.1829000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.03999999999999981</v>
       </c>
       <c r="I9" t="n">
-        <v>0.133</v>
+        <v>0.1427</v>
       </c>
       <c r="J9" t="n">
-        <v>2.053</v>
+        <v>2.1112</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9425000000000001</v>
+        <v>0.9672999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1104</v>
+        <v>1.1439</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8699</v>
+        <v>-1.9284</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8925</v>
+        <v>-0.9273</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9773999999999999</v>
+        <v>-1.0011</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4096</v>
+        <v>0.405</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6032</v>
+        <v>-0.5985</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.048</v>
+        <v>-1.0245</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4447</v>
+        <v>0.426</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7262000000000001</v>
+        <v>-0.7527999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9068</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.2475</v>
+        <v>-6.3468</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.948</v>
+        <v>-5.782299999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2996</v>
+        <v>-0.5644</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.412100000000001</v>
+        <v>-5.4506</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0491</v>
+        <v>-2.0743</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.363</v>
+        <v>-3.3763</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.879</v>
+        <v>-3.7907</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2395</v>
+        <v>-1.1886</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6395</v>
+        <v>-2.6021</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.533</v>
+        <v>-1.6598</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8095000000000001</v>
+        <v>-0.8855999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7235</v>
+        <v>-0.7742</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6146</v>
+        <v>0.6073</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R10" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8001</v>
+        <v>2.7811</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3725</v>
+        <v>1.4095</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4276</v>
+        <v>1.3717</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.2501</v>
+        <v>-4.284800000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.393</v>
+        <v>-1.3767</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8572</v>
+        <v>-2.9081</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.4489</v>
+        <v>-7.4417</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.5505</v>
+        <v>-7.299899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1018000000000001</v>
+        <v>-0.1417999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.363200000000001</v>
+        <v>-6.3461</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.8058</v>
+        <v>-5.792400000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5574</v>
+        <v>-0.5537000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1659</v>
+        <v>-3.0168</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.9127</v>
+        <v>-4.827500000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7467</v>
+        <v>1.8107</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1972</v>
+        <v>-3.3293</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.893</v>
+        <v>-0.9649</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3041</v>
+        <v>-2.3644</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6872</v>
+        <v>3.6442</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9789</v>
+        <v>-0.9526000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.3732</v>
+        <v>-2.3071</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3945</v>
+        <v>1.3545</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5408</v>
+        <v>-1.5601</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7828</v>
+        <v>-1.8111</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2942</v>
+        <v>-8.2637</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.7977</v>
+        <v>-8.920299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5037</v>
+        <v>0.6566999999999994</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.385200000000001</v>
+        <v>-9.317299999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.6143</v>
+        <v>-9.494600000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2287999999999991</v>
+        <v>0.1768000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>7.5634</v>
+        <v>8.559800000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.704000000000001</v>
+        <v>-5.0726</v>
       </c>
       <c r="L12" t="n">
-        <v>13.2673</v>
+        <v>13.6325</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.9486</v>
+        <v>-17.877</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.91</v>
+        <v>-4.4213</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.0382</v>
+        <v>-13.4557</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.097</v>
+        <v>-4.048999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-26.63</v>
+        <v>-26.319</v>
       </c>
       <c r="R12" t="n">
-        <v>22.5329</v>
+        <v>22.2701</v>
       </c>
       <c r="S12" t="n">
-        <v>8.033700000000001</v>
+        <v>7.9847</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8679</v>
+        <v>-3.508199999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>11.9014</v>
+        <v>11.493</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.8453</v>
+        <v>-2.882400000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>12.1372</v>
+        <v>12.3463</v>
       </c>
       <c r="X12" t="n">
-        <v>-14.9826</v>
+        <v>-15.2287</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLÍNICA PONFERRADA SDP.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CLÍNICA PONFERRADA SDP.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.031</v>
+        <v>5.2865</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0768</v>
+        <v>3.9056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9542</v>
+        <v>1.3809</v>
       </c>
       <c r="G2" t="n">
         <v>3.8673</v>
@@ -610,13 +610,13 @@
         <v>3.4417</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0989</v>
+        <v>0.1565</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.3193</v>
+        <v>-1.4904</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2204</v>
+        <v>1.647</v>
       </c>
       <c r="V2" t="n">
         <v>2.8823</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7383</v>
+        <v>3.3445</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5725</v>
+        <v>1.1556</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1657</v>
+        <v>2.1889</v>
       </c>
       <c r="G3" t="n">
         <v>1.5033</v>
@@ -688,13 +688,13 @@
         <v>4.2515</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0098</v>
+        <v>1.616</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0406</v>
+        <v>-0.4575</v>
       </c>
       <c r="U3" t="n">
-        <v>2.0503</v>
+        <v>2.0735</v>
       </c>
       <c r="V3" t="n">
         <v>0.2251000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6916</v>
+        <v>1.936</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3732</v>
+        <v>2.3351</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6816</v>
+        <v>-0.3991</v>
       </c>
       <c r="G4" t="n">
         <v>2.0476</v>
@@ -766,13 +766,13 @@
         <v>0.6074000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3729</v>
+        <v>0.6172</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3079</v>
+        <v>0.2698</v>
       </c>
       <c r="U4" t="n">
-        <v>0.065</v>
+        <v>0.3475</v>
       </c>
       <c r="V4" t="n">
         <v>0.6883</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8485</v>
+        <v>0.3685</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5514</v>
+        <v>0.8903</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7029</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0544</v>
+        <v>-0.0444</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.395</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1456</v>
+        <v>0.3505</v>
       </c>
       <c r="J5" t="n">
-        <v>1.074</v>
+        <v>0.7176</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3174000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3914</v>
+        <v>0.6596</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1284</v>
+        <v>-0.7619</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5912999999999999</v>
+        <v>-0.4529</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5371</v>
+        <v>-0.3091</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2024</v>
+        <v>1.2148</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0123</v>
+        <v>-0.2025</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8099000000000001</v>
+        <v>1.4172</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1052</v>
+        <v>0.3884</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9877</v>
+        <v>0.3752</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1175</v>
+        <v>0.01319999999999999</v>
       </c>
       <c r="V5" t="n">
+        <v>-1.1902</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.5019</v>
-      </c>
       <c r="X5" t="n">
-        <v>-0.5019</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1926999999999999</v>
+        <v>-0.322</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4535</v>
+        <v>0.617</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6461</v>
+        <v>-0.9390999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2028</v>
+        <v>-1.0544</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1311</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0716</v>
+        <v>-0.1456</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2157</v>
+        <v>1.074</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8180000000000001</v>
+        <v>-0.3174000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0336</v>
+        <v>1.3914</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4184</v>
+        <v>-2.1284</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3131</v>
+        <v>-0.5912999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1053</v>
+        <v>-1.5371</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6442</v>
+        <v>-0.2024</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.2883</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6441</v>
+        <v>0.8099000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7136</v>
+        <v>0.9348</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9839</v>
+        <v>0.0534</v>
       </c>
       <c r="U6" t="n">
-        <v>2.7297</v>
+        <v>0.8814000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3258</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6351</v>
+        <v>0.5019</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3092</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5826</v>
+        <v>-0.8995000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>-1.4143</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8318</v>
+        <v>0.5147999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8201</v>
@@ -1000,13 +1000,13 @@
         <v>1.4172</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2388</v>
+        <v>0.9218999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>-0.194</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4328</v>
+        <v>1.1158</v>
       </c>
       <c r="V7" t="n">
         <v>-1.216</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6066</v>
+        <v>-1.4039</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2034</v>
+        <v>-3.5315</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8099000000000001</v>
+        <v>2.1275</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0444</v>
+        <v>-2.2028</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.395</v>
+        <v>-1.1311</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3505</v>
+        <v>-1.0716</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7176</v>
+        <v>0.2157</v>
       </c>
       <c r="K8" t="n">
-        <v>0.058</v>
+        <v>-0.8180000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6596</v>
+        <v>1.0336</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7619</v>
+        <v>-2.4184</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4529</v>
+        <v>-0.3131</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3091</v>
+        <v>-2.1053</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2148</v>
+        <v>-3.6442</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2025</v>
+        <v>-7.2883</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4172</v>
+        <v>3.6441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5867</v>
+        <v>2.117</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3117</v>
+        <v>-0.09400000000000003</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2749</v>
+        <v>2.211</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1902</v>
+        <v>2.3258</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.6351</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1902</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7881</v>
+        <v>-2.344</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2524000000000002</v>
+        <v>0.6675999999999997</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0405</v>
+        <v>-3.0117</v>
       </c>
       <c r="G9" t="n">
         <v>0.1829000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.405</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5985</v>
+        <v>-0.1544</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0245</v>
+        <v>-0.6093000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.426</v>
+        <v>0.4548</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7527999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3468</v>
+        <v>-5.2392</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.782299999999999</v>
+        <v>-5.846500000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5644</v>
+        <v>0.6073000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.4506</v>
+        <v>-6.3461</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0743</v>
+        <v>-5.792400000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3763</v>
+        <v>-0.5537000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.7907</v>
+        <v>-3.0168</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1886</v>
+        <v>-4.827500000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6021</v>
+        <v>1.8107</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6598</v>
+        <v>-3.3293</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8855999999999999</v>
+        <v>-0.9649</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7742</v>
+        <v>-2.3644</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6073</v>
+        <v>1.4172</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0245</v>
+        <v>-2.227</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6319</v>
+        <v>3.6442</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7811</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4095</v>
+        <v>-0.8536</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3717</v>
+        <v>2.1036</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.284800000000001</v>
+        <v>-1.5601</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.3767</v>
+        <v>0.2509</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9081</v>
+        <v>-1.8111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.4417</v>
+        <v>-7.9782</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.299899999999999</v>
+        <v>-7.3794</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1417999999999999</v>
+        <v>-0.5988</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.3461</v>
+        <v>-5.4506</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.792400000000001</v>
+        <v>-2.0743</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5537000000000001</v>
+        <v>-3.3763</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0168</v>
+        <v>-3.7907</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.827500000000001</v>
+        <v>-1.1886</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8107</v>
+        <v>-2.6021</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3293</v>
+        <v>-1.6598</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9649</v>
+        <v>-0.8855999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3644</v>
+        <v>-0.7742</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4172</v>
+        <v>0.6073</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.227</v>
+        <v>-2.0245</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6442</v>
+        <v>2.6319</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9526000000000001</v>
+        <v>1.1497</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.3071</v>
+        <v>-0.1875</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3545</v>
+        <v>1.3372</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5601</v>
+        <v>-4.284800000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2509</v>
+        <v>-1.3767</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8111</v>
+        <v>-2.9081</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2637</v>
+        <v>-7.2513</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.920299999999999</v>
+        <v>-8.6005</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6566999999999994</v>
+        <v>1.349</v>
       </c>
       <c r="G12" t="n">
         <v>-9.317299999999999</v>
@@ -1390,13 +1390,13 @@
         <v>22.2701</v>
       </c>
       <c r="S12" t="n">
-        <v>7.9847</v>
+        <v>8.9971</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.508199999999999</v>
+        <v>-3.1879</v>
       </c>
       <c r="U12" t="n">
-        <v>11.493</v>
+        <v>12.185</v>
       </c>
       <c r="V12" t="n">
         <v>-2.882400000000001</v>
